--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93418</v>
+        <v>93421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93418</v>
+        <v>93421</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93421</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93427</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93427</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91887</v>
+        <v>91889</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>127756236</v>
       </c>
       <c r="B30" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>136261579</v>
       </c>
       <c r="B31" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>136261392</v>
       </c>
       <c r="B38" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -2543,7 +2543,7 @@
         <v>136424364</v>
       </c>
       <c r="B18" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         <v>136424425</v>
       </c>
       <c r="B19" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4092,54 +4092,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>62134717</v>
+        <v>137429821</v>
       </c>
       <c r="B32" t="n">
-        <v>92869</v>
+        <v>93499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>Bässe Storåsens sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>599336</v>
+        <v>599350</v>
       </c>
       <c r="R32" t="n">
-        <v>6820724</v>
+        <v>6820651</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4166,12 +4164,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Början på gamla basvägen väster om vändplan ned mot bäcken känd lokal</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4180,60 +4183,56 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>frodig äldre lågörtsgranskog</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134717</t>
+          <t>https://artportalen.se/Sighting/137429821</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>62134720</v>
+        <v>62134717</v>
       </c>
       <c r="B33" t="n">
-        <v>91443</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4252,10 +4251,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>599421</v>
+        <v>599336</v>
       </c>
       <c r="R33" t="n">
-        <v>6820637</v>
+        <v>6820724</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4290,11 +4289,6 @@
           <t>2016-09-27</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>konfirmerad av Lennart Söderberg</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4306,7 +4300,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>äldre kalkpåverkad lågörtsgranskog</t>
+          <t>frodig äldre lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4323,13 +4317,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134720</t>
+          <t>https://artportalen.se/Sighting/62134717</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>103359356</v>
+        <v>62134720</v>
       </c>
       <c r="B34" t="n">
         <v>91443</v>
@@ -4357,17 +4351,26 @@
           <t>(Bres.) Corner</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bässeravinen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>599422</v>
+        <v>599421</v>
       </c>
       <c r="R34" t="n">
-        <v>6820636</v>
+        <v>6820637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4394,12 +4397,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-08-27</t>
+          <t>2016-09-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>konfirmerad av Lennart Söderberg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4410,28 +4418,33 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre kalkpåverkad lågörtsgranskog</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tomas Troschke</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103359356</t>
+          <t>https://artportalen.se/Sighting/62134720</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112306179</v>
+        <v>103359356</v>
       </c>
       <c r="B35" t="n">
         <v>91443</v>
@@ -4460,23 +4473,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storåsens sydsluttning  söder om myren, Hls</t>
+          <t>Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>599448</v>
+        <v>599422</v>
       </c>
       <c r="R35" t="n">
-        <v>6820628</v>
+        <v>6820636</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4503,17 +4509,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Där stigen delar sig ned mot myren</t>
+          <t>2022-08-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4522,41 +4523,30 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Barrblandskog kalkpåverkad.</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Tomas Troschke</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112306179</t>
+          <t>https://artportalen.se/Sighting/103359356</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119358627</v>
+        <v>112306179</v>
       </c>
       <c r="B36" t="n">
         <v>91443</v>
@@ -4594,14 +4584,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Storåsens sydsluttning  söder om myren, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>599420</v>
+        <v>599448</v>
       </c>
       <c r="R36" t="n">
-        <v>6820647</v>
+        <v>6820628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4628,17 +4618,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På samma plats som dofttaggsvampen</t>
+          <t>Där stigen delar sig ned mot myren</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4658,7 +4648,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+          <t>Barrblandskog kalkpåverkad.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4675,13 +4665,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119358627</t>
+          <t>https://artportalen.se/Sighting/112306179</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119840701</v>
+        <v>119358627</v>
       </c>
       <c r="B37" t="n">
         <v>91443</v>
@@ -4710,19 +4700,23 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>599416</v>
+        <v>599420</v>
       </c>
       <c r="R37" t="n">
-        <v>6820643</v>
+        <v>6820647</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4749,12 +4743,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På samma plats som dofttaggsvampen</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4772,6 +4771,11 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Barrblandskog örtrik delvis kalkgynnad.</t>
+        </is>
+      </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
@@ -4786,16 +4790,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119840701</t>
+          <t>https://artportalen.se/Sighting/119358627</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136261392</v>
+        <v>119840701</v>
       </c>
       <c r="B38" t="n">
-        <v>91630</v>
+        <v>91443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4826,14 +4830,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>599408</v>
+        <v>599416</v>
       </c>
       <c r="R38" t="n">
-        <v>6820625</v>
+        <v>6820643</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4860,12 +4864,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4878,79 +4882,76 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136261392</t>
+          <t>https://artportalen.se/Sighting/119840701</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119416410</v>
+        <v>136261392</v>
       </c>
       <c r="B39" t="n">
-        <v>92928</v>
+        <v>91630</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5836</v>
+        <v>5754</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>norr om myren Bässeravinen, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>599347</v>
+        <v>599408</v>
       </c>
       <c r="R39" t="n">
-        <v>6820675</v>
+        <v>6820625</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4974,12 +4975,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5006,38 +5007,38 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119416410</t>
+          <t>https://artportalen.se/Sighting/136261392</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>62134715</v>
+        <v>119416410</v>
       </c>
       <c r="B40" t="n">
-        <v>93233</v>
+        <v>92928</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5047,22 +5048,24 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>N om Bässeravinen, Hls</t>
+          <t>norr om myren Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>599343</v>
+        <v>599347</v>
       </c>
       <c r="R40" t="n">
-        <v>6820701</v>
+        <v>6820675</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5086,12 +5089,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2016-09-27</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5104,32 +5107,27 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
-        </is>
-      </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134715</t>
+          <t>https://artportalen.se/Sighting/119416410</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>62134718</v>
+        <v>62134715</v>
       </c>
       <c r="B41" t="n">
         <v>93233</v>
@@ -5159,7 +5157,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5173,10 +5171,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>599396</v>
+        <v>599343</v>
       </c>
       <c r="R41" t="n">
-        <v>6820634</v>
+        <v>6820701</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5223,7 +5221,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>mossvacka i äldre lågörtsgranskog</t>
+          <t>rel gammal kalkpåverkad lågörtsgranskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5240,13 +5238,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62134718</t>
+          <t>https://artportalen.se/Sighting/62134715</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119840695</v>
+        <v>62134718</v>
       </c>
       <c r="B42" t="n">
         <v>93233</v>
@@ -5274,20 +5272,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bässe söder om stigen, Hls</t>
+          <t>N om Bässeravinen, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>599416</v>
+        <v>599396</v>
       </c>
       <c r="R42" t="n">
-        <v>6820643</v>
+        <v>6820634</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5314,12 +5318,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2016-09-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5332,27 +5336,32 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>mossvacka i äldre lågörtsgranskog</t>
+        </is>
+      </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119840695</t>
+          <t>https://artportalen.se/Sighting/62134718</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120315881</v>
+        <v>119840695</v>
       </c>
       <c r="B43" t="n">
         <v>93233</v>
@@ -5380,28 +5389,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bässe, Hls</t>
+          <t>Bässe söder om stigen, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>599420</v>
+        <v>599416</v>
       </c>
       <c r="R43" t="n">
-        <v>6820647</v>
+        <v>6820643</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5428,12 +5429,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5460,16 +5461,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120315881</t>
+          <t>https://artportalen.se/Sighting/119840695</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128377662</v>
+        <v>120315881</v>
       </c>
       <c r="B44" t="n">
-        <v>93307</v>
+        <v>93233</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5494,20 +5495,28 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bässe Storåsen sydsluttning, Hls</t>
+          <t>Bässe, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>599342</v>
+        <v>599420</v>
       </c>
       <c r="R44" t="n">
-        <v>6820709</v>
+        <v>6820647</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5534,12 +5543,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5555,27 +5564,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128377662</t>
+          <t>https://artportalen.se/Sighting/120315881</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>68784057</v>
+        <v>128377662</v>
       </c>
       <c r="B45" t="n">
-        <v>75428</v>
+        <v>93307</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5583,37 +5592,40 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>Bässe Storåsen sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>599424</v>
+        <v>599342</v>
       </c>
       <c r="R45" t="n">
-        <v>6820802</v>
+        <v>6820709</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5637,12 +5649,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5651,46 +5663,34 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>rel tät, högstammig granskog i sydlut</t>
-        </is>
-      </c>
-      <c r="AN45" t="n">
-        <v>100</v>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>100 substratenheter # ca 120-åriga granar</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68784057</t>
+          <t>https://artportalen.se/Sighting/128377662</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>82307781</v>
+        <v>68784057</v>
       </c>
       <c r="B46" t="n">
-        <v>79946</v>
+        <v>75428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5698,41 +5698,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6426</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bässe myren norra kanten, Hls</t>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>599371</v>
+        <v>599424</v>
       </c>
       <c r="R46" t="n">
-        <v>6820587</v>
+        <v>6820802</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5759,12 +5752,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2020-02-21</t>
+          <t>2017-07-07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5773,49 +5766,46 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Blandmyr med barrträd</t>
-        </is>
-      </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>Mindre myr med källdråg och tjärvedstubbar</t>
-        </is>
+          <t>rel tät, högstammig granskog i sydlut</t>
+        </is>
+      </c>
+      <c r="AN46" t="n">
+        <v>100</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Tjärvedstubbe  av tall</t>
+          <t>100 substratenheter # ca 120-åriga granar</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alf Bjarne Roland Pallin</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82307781</t>
+          <t>https://artportalen.se/Sighting/68784057</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>102521833</v>
+        <v>82307781</v>
       </c>
       <c r="B47" t="n">
-        <v>57953</v>
+        <v>79946</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5823,45 +5813,41 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>A 13021- 2022, Hls</t>
+          <t>Bässe myren norra kanten, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>599338</v>
+        <v>599371</v>
       </c>
       <c r="R47" t="n">
-        <v>6820891</v>
+        <v>6820587</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5888,22 +5874,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2022-07-28</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2020-02-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5912,33 +5888,49 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Blandmyr med barrträd</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Mindre myr med källdråg och tjärvedstubbar</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Tjärvedstubbe  av tall</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Alf Bjarne Roland Pallin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102521833</t>
+          <t>https://artportalen.se/Sighting/82307781</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>102521837</v>
+        <v>102521833</v>
       </c>
       <c r="B48" t="n">
-        <v>58114</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5946,21 +5938,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6016,7 +6008,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6026,7 +6018,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6052,60 +6044,62 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102521837</t>
+          <t>https://artportalen.se/Sighting/102521833</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>68784055</v>
+        <v>102521837</v>
       </c>
       <c r="B49" t="n">
-        <v>99142</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+          <t>A 13021- 2022, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>599340</v>
+        <v>599338</v>
       </c>
       <c r="R49" t="n">
-        <v>6820725</v>
+        <v>6820891</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6132,12 +6126,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2017-07-07</t>
+          <t>2022-07-28</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6148,36 +6152,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/68784055</t>
+          <t>https://artportalen.se/Sighting/102521837</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>68784056</v>
+        <v>68784055</v>
       </c>
       <c r="B50" t="n">
-        <v>99036</v>
+        <v>99142</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6185,26 +6184,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>223591</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6218,10 +6217,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>599297</v>
+        <v>599340</v>
       </c>
       <c r="R50" t="n">
-        <v>6820782</v>
+        <v>6820725</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6267,7 +6266,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>högstammig ca 110-årig granskog i sydsluttning</t>
+          <t>högvuxen 100-150-årig rikörtsgranskog i nederdelen av sydsluttning</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
@@ -6283,6 +6282,122 @@
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68784055</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>68784056</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bässeravinen, Storåsens sydsluttning, Hls</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>599297</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6820782</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Enånger</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>högstammig ca 110-årig granskog i sydsluttning</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/68784056</t>
         </is>
@@ -6339,6 +6454,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4095,7 +4095,7 @@
         <v>137429821</v>
       </c>
       <c r="B32" t="n">
-        <v>93499</v>
+        <v>93500</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4095,7 +4095,7 @@
         <v>137429821</v>
       </c>
       <c r="B32" t="n">
-        <v>93500</v>
+        <v>93503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 13021-2022 artfynd.xlsx
+++ b/artfynd/A 13021-2022 artfynd.xlsx
@@ -4095,7 +4095,7 @@
         <v>137429821</v>
       </c>
       <c r="B32" t="n">
-        <v>93503</v>
+        <v>93507</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
